--- a/data/trans_orig/IP22D1_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP22D1_2023-Clase-trans_orig.xlsx
@@ -1794,7 +1794,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15077</t>
+          <t>15204</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32962</t>
+          <t>32496</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4803</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10267</t>
+          <t>9617</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20239</t>
+          <t>20682</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>3466</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>2547</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>46360</t>
+          <t>47707</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>95184</t>
+          <t>95155</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6393</t>
+          <t>5046</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4997</t>
+          <t>5026</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP22D1_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP22D1_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,64 +720,64 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3488</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6725</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>6629</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4085</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>10810</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3488</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3488</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3488</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>6725</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>6725</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6725</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>6629</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>6629</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>6629</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>10810</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10810</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10810</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,64 +1063,64 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4872</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5647</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>5883</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5319</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>10967</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>4872</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>4872</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>4872</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>5647</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>5647</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>5647</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>10967</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10967</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10967</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,64 +1406,64 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7645</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3379</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3154</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>8101</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>11480</t>
+          <t>10799</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7645</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7645</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>7645</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>3379</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>3379</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3379</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>11480</t>
+          <t>10799</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11480</t>
+          <t>10799</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11480</t>
+          <t>10799</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>16854</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>13330</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>17798</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>94,7%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>74,9%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>17969</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>12239</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>18955</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>15204</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>19880</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>95,35%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,27 +1824,27 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>36924</t>
+          <t>29093</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32496</t>
+          <t>24471</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37849</t>
+          <t>30037</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1862,107 +1862,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>944</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4468</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4676</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>4,65%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>5566</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>3,14%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>23,52%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>5353</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>18,53%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>17798</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>17798</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>17798</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>17969</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>17969</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>17969</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19880</t>
+          <t>12239</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19880</t>
+          <t>12239</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19880</t>
+          <t>12239</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>37849</t>
+          <t>30037</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>37849</t>
+          <t>30037</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>37849</t>
+          <t>30037</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11667</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9740</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>12076</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>96,62%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>80,65%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>10146</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>10575</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>12560</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>9617</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>13083</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>96,0%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,27 +2167,27 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>22706</t>
+          <t>22242</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20682</t>
+          <t>20190</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23229</t>
+          <t>22651</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2205,107 +2205,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>409</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
+          <t>3,38%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>523</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>3466</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>4,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>2461</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>26,5%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>523</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>2547</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>12076</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>12076</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>12076</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>10146</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>10146</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>10146</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>13083</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13083</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13083</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>23229</t>
+          <t>22651</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>23229</t>
+          <t>22651</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>23229</t>
+          <t>22651</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,64 +2435,64 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2171</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>3561</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>3785</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>2285</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>5956</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2171</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>2171</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2171</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>3561</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>3561</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>3561</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>5956</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>5956</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>5956</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>46697</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>43110</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>48050</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>97,19%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>89,72%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>47427</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>42264</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>51305</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>47707</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>52753</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>97,25%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,27 +2853,27 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>98733</t>
+          <t>88961</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>95155</t>
+          <t>85524</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>100181</t>
+          <t>90314</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2891,107 +2891,107 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4940</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
+          <t>2,81%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>1448</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>5046</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>2,75%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>4790</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>9,57%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1448</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>5026</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>48050</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>48050</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>48050</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>47427</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>47427</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>47427</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>52753</t>
+          <t>42264</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>52753</t>
+          <t>42264</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>52753</t>
+          <t>42264</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>100181</t>
+          <t>90314</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>100181</t>
+          <t>90314</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>100181</t>
+          <t>90314</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
